--- a/output/c4ai_produtividade_todos_grupos.xlsx
+++ b/output/c4ai_produtividade_todos_grupos.xlsx
@@ -475,107 +475,107 @@
         <v>28.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGRIBIO</t>
+          <t>KEML</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KEML</t>
+          <t>AI HEALTH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI HEALTH</t>
+          <t>HUMANITIES</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>13.25</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.04</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HUMANITIES</t>
+          <t>AGRIBIO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D6" t="n">
         <v>2024</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.25</v>
+        <v>10.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.87</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="7">
@@ -600,7 +600,7 @@
         <v>10.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>7.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">

--- a/output/c4ai_produtividade_todos_grupos.xlsx
+++ b/output/c4ai_produtividade_todos_grupos.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
         <v>2020</v>
@@ -572,10 +572,10 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>5.59</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="7">
